--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-29T10:34:12.363Z</t>
+    <t>2026-10-01T11:06:32.300Z</t>
   </si>
   <si>
     <t>Insurance and Care NSW | icare</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-01T11:06:32.300Z</t>
+    <t>2026-10-01T12:02:13.110Z</t>
   </si>
   <si>
     <t>Insurance and Care NSW | icare</t>
